--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.60088625683631</v>
+        <v>8.060144016735901</v>
       </c>
       <c r="D2" t="n">
-        <v>49.32424466281257</v>
+        <v>8.015189757707043</v>
       </c>
       <c r="E2" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F2" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.18050740221081</v>
+        <v>9.616832452859256</v>
       </c>
       <c r="D3" t="n">
-        <v>59.66499516671902</v>
+        <v>9.695561714591841</v>
       </c>
       <c r="E3" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F3" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.78123127756751</v>
+        <v>8.901950082604721</v>
       </c>
       <c r="D4" t="n">
-        <v>53.97467688165875</v>
+        <v>8.770884993269547</v>
       </c>
       <c r="E4" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F4" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.83536610540316</v>
+        <v>6.473246992128014</v>
       </c>
       <c r="D5" t="n">
-        <v>39.61194128895166</v>
+        <v>6.436940459454646</v>
       </c>
       <c r="E5" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F5" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.3312740148592</v>
+        <v>9.47883202741462</v>
       </c>
       <c r="D6" t="n">
-        <v>58.96653523055748</v>
+        <v>9.58206197496559</v>
       </c>
       <c r="E6" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F6" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.80979568687077</v>
+        <v>7.7690917991165</v>
       </c>
       <c r="D7" t="n">
-        <v>48.36223941980322</v>
+        <v>7.858863905718023</v>
       </c>
       <c r="E7" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F7" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.56247970472956</v>
+        <v>4.803902952018554</v>
       </c>
       <c r="D8" t="n">
-        <v>29.10159551031724</v>
+        <v>4.729009270426552</v>
       </c>
       <c r="E8" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F8" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.51946212816767</v>
+        <v>4.309412595827247</v>
       </c>
       <c r="D9" t="n">
-        <v>25.33611521922204</v>
+        <v>4.117118723123582</v>
       </c>
       <c r="E9" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F9" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.4757865583539</v>
+        <v>6.414815315732509</v>
       </c>
       <c r="D10" t="n">
-        <v>38.73606362157742</v>
+        <v>6.29461033850633</v>
       </c>
       <c r="E10" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F10" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.92511340628165</v>
+        <v>6.650330928520769</v>
       </c>
       <c r="D11" t="n">
-        <v>39.81248740795388</v>
+        <v>6.469529203792506</v>
       </c>
       <c r="E11" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F11" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.92323477725382</v>
+        <v>3.562525651303746</v>
       </c>
       <c r="D12" t="n">
-        <v>22.02771814387073</v>
+        <v>3.579504198378993</v>
       </c>
       <c r="E12" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F12" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>51.58611605057472</v>
+        <v>8.382743858218394</v>
       </c>
       <c r="D13" t="n">
-        <v>52.25525949942186</v>
+        <v>8.491479668656053</v>
       </c>
       <c r="E13" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F13" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.30039876094473</v>
+        <v>3.136314798653518</v>
       </c>
       <c r="D14" t="n">
-        <v>18.08789774430254</v>
+        <v>2.939283383449164</v>
       </c>
       <c r="E14" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F14" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.65271514863333</v>
+        <v>3.031066211652916</v>
       </c>
       <c r="D15" t="n">
-        <v>19.16266721968396</v>
+        <v>3.113933423198644</v>
       </c>
       <c r="E15" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F15" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.94105519805558</v>
+        <v>5.027921469684032</v>
       </c>
       <c r="D16" t="n">
-        <v>31.52770434412572</v>
+        <v>5.12325195592043</v>
       </c>
       <c r="E16" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F16" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39.48120751883026</v>
+        <v>6.415696221809918</v>
       </c>
       <c r="D17" t="n">
-        <v>40.16031452320274</v>
+        <v>6.526051110020446</v>
       </c>
       <c r="E17" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F17" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>53.69061686258669</v>
+        <v>8.724725240170338</v>
       </c>
       <c r="D18" t="n">
-        <v>54.39691206498836</v>
+        <v>8.83949821056061</v>
       </c>
       <c r="E18" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F18" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>19.14374734679793</v>
+        <v>3.110858943854665</v>
       </c>
       <c r="D19" t="n">
-        <v>19.7888828548586</v>
+        <v>3.215693463914523</v>
       </c>
       <c r="E19" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F19" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>16.59021936791176</v>
+        <v>2.695910647285661</v>
       </c>
       <c r="D20" t="n">
-        <v>15.88858091744749</v>
+        <v>2.581894399085217</v>
       </c>
       <c r="E20" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F20" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>57.30766621354564</v>
+        <v>9.312495759701166</v>
       </c>
       <c r="D21" t="n">
-        <v>58.0342803322004</v>
+        <v>9.430570553982566</v>
       </c>
       <c r="E21" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F21" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>6.367438837922732</v>
+        <v>1.034708811162444</v>
       </c>
       <c r="D22" t="n">
-        <v>5.640751073153535</v>
+        <v>0.9166220493874494</v>
       </c>
       <c r="E22" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F22" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>13.86217102391913</v>
+        <v>2.252602791386858</v>
       </c>
       <c r="D23" t="n">
-        <v>13.91830450638449</v>
+        <v>2.261724482287479</v>
       </c>
       <c r="E23" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F23" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>25.79717826857391</v>
+        <v>4.19204146864326</v>
       </c>
       <c r="D24" t="n">
-        <v>25.09107032335404</v>
+        <v>4.077298927545032</v>
       </c>
       <c r="E24" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F24" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>39.33451202917811</v>
+        <v>6.391858204741443</v>
       </c>
       <c r="D25" t="n">
-        <v>39.19108901767222</v>
+        <v>6.368551965371736</v>
       </c>
       <c r="E25" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F25" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>11.23118546649622</v>
+        <v>1.825067638305636</v>
       </c>
       <c r="D26" t="n">
-        <v>12.33627886255677</v>
+        <v>2.004645315165475</v>
       </c>
       <c r="E26" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F26" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>21.77257182056856</v>
+        <v>3.538042920842392</v>
       </c>
       <c r="D27" t="n">
-        <v>22.73527857543334</v>
+        <v>3.694482768507918</v>
       </c>
       <c r="E27" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F27" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>24.12700443905484</v>
+        <v>3.920638221346412</v>
       </c>
       <c r="D28" t="n">
-        <v>23.80322179329975</v>
+        <v>3.86802354141121</v>
       </c>
       <c r="E28" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F28" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>18.36196680993447</v>
+        <v>2.983819606614351</v>
       </c>
       <c r="D29" t="n">
-        <v>18.40998793043654</v>
+        <v>2.991623038695937</v>
       </c>
       <c r="E29" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F29" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>24.28672704858229</v>
+        <v>3.946593145394622</v>
       </c>
       <c r="D30" t="n">
-        <v>25.47084513577849</v>
+        <v>4.139012334564005</v>
       </c>
       <c r="E30" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F30" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>50.67260188809828</v>
+        <v>8.23429780681597</v>
       </c>
       <c r="D31" t="n">
-        <v>51.35765512447567</v>
+        <v>8.345618957727297</v>
       </c>
       <c r="E31" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F31" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>51.75080660874157</v>
+        <v>8.409506073920506</v>
       </c>
       <c r="D32" t="n">
-        <v>51.26174799044011</v>
+        <v>8.330034048446519</v>
       </c>
       <c r="E32" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F32" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>43.07149129011545</v>
+        <v>6.999117334643762</v>
       </c>
       <c r="D33" t="n">
-        <v>43.86703636874513</v>
+        <v>7.128393409921085</v>
       </c>
       <c r="E33" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F33" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>50.48645175236359</v>
+        <v>8.204048409759084</v>
       </c>
       <c r="D34" t="n">
-        <v>50.96734314336707</v>
+        <v>8.282193260797149</v>
       </c>
       <c r="E34" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F34" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>36.89407335915971</v>
+        <v>5.995286920863453</v>
       </c>
       <c r="D35" t="n">
-        <v>38.10447247221745</v>
+        <v>6.191976776735336</v>
       </c>
       <c r="E35" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F35" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>40.86501103499945</v>
+        <v>6.640564293187412</v>
       </c>
       <c r="D36" t="n">
-        <v>40.78257034553683</v>
+        <v>6.627167681149734</v>
       </c>
       <c r="E36" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F36" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>20.41603561427761</v>
+        <v>3.317605787320112</v>
       </c>
       <c r="D37" t="n">
-        <v>20.96969486890392</v>
+        <v>3.407575416196887</v>
       </c>
       <c r="E37" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F37" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>64.38388308917244</v>
+        <v>10.46238100199052</v>
       </c>
       <c r="D38" t="n">
-        <v>64.9225167418162</v>
+        <v>10.54990897054513</v>
       </c>
       <c r="E38" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F38" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>60.16210436788595</v>
+        <v>9.776341959781467</v>
       </c>
       <c r="D39" t="n">
-        <v>60.61601030139174</v>
+        <v>9.850101673976157</v>
       </c>
       <c r="E39" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F39" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>59.82917562352355</v>
+        <v>9.722241038822578</v>
       </c>
       <c r="D40" t="n">
-        <v>59.61161391769178</v>
+        <v>9.686887261624916</v>
       </c>
       <c r="E40" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F40" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>85.43409427754429</v>
+        <v>13.88304032010095</v>
       </c>
       <c r="D41" t="n">
-        <v>85.89436343961832</v>
+        <v>13.95783405893798</v>
       </c>
       <c r="E41" t="n">
-        <v>17.66836383260243</v>
+        <v>2.871109122797895</v>
       </c>
       <c r="F41" t="n">
-        <v>17.79859694064839</v>
+        <v>2.892272002855364</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
